--- a/artfynd/A 17190-2021 artfynd.xlsx
+++ b/artfynd/A 17190-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17190-2021 artfynd.xlsx
+++ b/artfynd/A 17190-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>1842831</v>
       </c>
       <c r="B2" t="n">
-        <v>89454</v>
+        <v>89464</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 17190-2021 artfynd.xlsx
+++ b/artfynd/A 17190-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>1842831</v>
       </c>
       <c r="B2" t="n">
-        <v>89464</v>
+        <v>89476</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 17190-2021 artfynd.xlsx
+++ b/artfynd/A 17190-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>1842831</v>
       </c>
       <c r="B2" t="n">
-        <v>89476</v>
+        <v>89480</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 17190-2021 artfynd.xlsx
+++ b/artfynd/A 17190-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>1842831</v>
       </c>
       <c r="B2" t="n">
-        <v>89480</v>
+        <v>89485</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>6276</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Goliatmusseron</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 17190-2021 artfynd.xlsx
+++ b/artfynd/A 17190-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>1842831</v>
       </c>
       <c r="B2" t="n">
-        <v>89485</v>
+        <v>89498</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>6276</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 17190-2021 artfynd.xlsx
+++ b/artfynd/A 17190-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>1842831</v>
       </c>
       <c r="B2" t="n">
-        <v>89498</v>
+        <v>89510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
